--- a/Python Tutorial.xlsx
+++ b/Python Tutorial.xlsx
@@ -28,6 +28,12 @@
 </t>
       </text>
     </comment>
+    <comment authorId="0" ref="F2">
+      <text>
+        <t xml:space="preserve">It is used to store data in key-values pairs.
+In some languages its called as map or associative array</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="D3">
       <text>
         <t xml:space="preserve">Why List is called Dynamic/Referential arrays
@@ -43,6 +49,15 @@
         <t xml:space="preserve">Ordered
 Immutable
 Multiple Duplicate Values</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F3">
+      <text>
+        <t xml:space="preserve">Mutable
+Indexing has no meaning
+Keys cant be duplicated
+Keys cant be mutable items
+Values can be mutable items</t>
       </text>
     </comment>
     <comment authorId="0" ref="E4">
@@ -53,6 +68,18 @@
 heterogeneous tuple
 2d tuple
 tuple type conversion
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F4">
+      <text>
+        <t xml:space="preserve">Empty Dictionary
+1d Dictionary
+With mixed keys
+2d Dictionary
+using list of tuples and Dict Func
+duplicate keys
+mutable items as keys
 </t>
       </text>
     </comment>
@@ -82,6 +109,12 @@
 slicing</t>
       </text>
     </comment>
+    <comment authorId="0" ref="F5">
+      <text>
+        <t xml:space="preserve">[ ]
+get</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="C6">
       <text>
         <t xml:space="preserve">indexing using step size
@@ -115,6 +148,14 @@
 Slicing</t>
       </text>
     </comment>
+    <comment authorId="0" ref="F7">
+      <text>
+        <t xml:space="preserve">pop
+popitem
+del 
+clear</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="C8">
       <text>
         <t xml:space="preserve">Arithmetic 
@@ -159,6 +200,13 @@
 </t>
       </text>
     </comment>
+    <comment authorId="0" ref="F9">
+      <text>
+        <t xml:space="preserve">Membership 
+Loop
+</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="C10">
       <text>
         <t xml:space="preserve">len
@@ -180,6 +228,16 @@
       <text>
         <t xml:space="preserve">count
 index
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F10">
+      <text>
+        <t xml:space="preserve">sum
+len
+max
+min 
+sorted
 </t>
       </text>
     </comment>
@@ -228,6 +286,11 @@
 a, b = b, a</t>
       </text>
     </comment>
+    <comment authorId="0" ref="F12">
+      <text>
+        <t xml:space="preserve">updating one dictionary with one dictionary</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="D13">
       <text>
         <t xml:space="preserve">count
@@ -238,6 +301,15 @@
 </t>
       </text>
     </comment>
+    <comment authorId="0" ref="F13">
+      <text>
+        <t xml:space="preserve">{keys : values for keys, values in dict.items()}
+print first 10 num and their squares
+using existing dictionary, convert KM to miles
+dict with if condition
+</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="D14">
       <text>
         <t xml:space="preserve">[expression for item in iterable if condition == True]</t>
@@ -246,6 +318,11 @@
     <comment authorId="0" ref="E14">
       <text>
         <t xml:space="preserve">Every set items are unique and they are immutable, however sets are mutable</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F14">
+      <text>
+        <t xml:space="preserve">map a list with temp and list with days in one dict with zip</t>
       </text>
     </comment>
     <comment authorId="0" ref="D15">
@@ -303,7 +380,7 @@
     <comment authorId="0" ref="E21">
       <text>
         <t xml:space="preserve">Union (|)
-Interaction (&amp;)
+Intersection (&amp;)
 Difference (-)
 Symmetric Difference (^)
 Membership test
@@ -324,7 +401,7 @@
     <comment authorId="0" ref="E23">
       <text>
         <t xml:space="preserve">Union/update
-Interaction / Interaction update
+Intersection / Intersection update
 Difference / Difference update
 Symmetric Difference /Symmetric Difference update
 Membership test
@@ -350,7 +427,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="127">
   <si>
     <t>Day - 1 (Basics)</t>
   </si>
@@ -376,7 +453,7 @@
     <t>Operators and its type</t>
   </si>
   <si>
-    <t>Strings</t>
+    <t>What are Strings</t>
   </si>
   <si>
     <t>What are Lists?</t>
@@ -385,6 +462,9 @@
     <t>What are Tuples?</t>
   </si>
   <si>
+    <t>What are Dictionaries?</t>
+  </si>
+  <si>
     <t>Python o/p - Print Function/ Error</t>
   </si>
   <si>
@@ -400,6 +480,9 @@
     <t>Characteristics of Tuple</t>
   </si>
   <si>
+    <t>Characteristics of Dictionary</t>
+  </si>
+  <si>
     <t>Data Types including complex numbers</t>
   </si>
   <si>
@@ -415,6 +498,9 @@
     <t>Creating Tuples</t>
   </si>
   <si>
+    <t>Creating Dictionary</t>
+  </si>
+  <si>
     <t>Type function</t>
   </si>
   <si>
@@ -430,6 +516,9 @@
     <t>Accessing items in tuple</t>
   </si>
   <si>
+    <t xml:space="preserve">Accessing items </t>
+  </si>
+  <si>
     <t>Variables</t>
   </si>
   <si>
@@ -445,6 +534,9 @@
     <t>Editing/Adding items to Tuple</t>
   </si>
   <si>
+    <t>Adding Key/Value pair</t>
+  </si>
+  <si>
     <t>Static vs Dynamic Typing</t>
   </si>
   <si>
@@ -460,6 +552,9 @@
     <t>Deleting Tuple</t>
   </si>
   <si>
+    <t>Removing Key/Value pair</t>
+  </si>
+  <si>
     <t>Static vs Dynamic Binding</t>
   </si>
   <si>
@@ -475,6 +570,9 @@
     <t>Operations on the Tuples</t>
   </si>
   <si>
+    <t>Editing Key/Value pair</t>
+  </si>
+  <si>
     <t>`</t>
   </si>
   <si>
@@ -493,6 +591,9 @@
     <t xml:space="preserve">common functions </t>
   </si>
   <si>
+    <t>Operations on the Dictionary</t>
+  </si>
+  <si>
     <t>Comments</t>
   </si>
   <si>
@@ -520,6 +621,9 @@
     <t>Difference between List/Tuple</t>
   </si>
   <si>
+    <t>items/keys/values</t>
+  </si>
+  <si>
     <t>Python Keywords/Identifiers</t>
   </si>
   <si>
@@ -532,6 +636,9 @@
     <t>Tuple Unpacking</t>
   </si>
   <si>
+    <t>update</t>
+  </si>
+  <si>
     <t>Rules of naming identifiers</t>
   </si>
   <si>
@@ -547,6 +654,9 @@
     <t>Zip</t>
   </si>
   <si>
+    <t>Dictionary comprehension</t>
+  </si>
+  <si>
     <t>User Input</t>
   </si>
   <si>
@@ -562,6 +672,9 @@
     <t>Sets</t>
   </si>
   <si>
+    <t>zip</t>
+  </si>
+  <si>
     <t>Addition of two numbers</t>
   </si>
   <si>
@@ -577,6 +690,9 @@
     <t>Characteristics of Sets</t>
   </si>
   <si>
+    <t>nested comprehension</t>
+  </si>
+  <si>
     <t>Type Conversion - Implicit/ Explicit</t>
   </si>
   <si>
@@ -592,6 +708,9 @@
     <t>Creating Sets</t>
   </si>
   <si>
+    <t>print a table of 1-4 using nested comprehension</t>
+  </si>
+  <si>
     <t>Literal</t>
   </si>
   <si>
@@ -629,9 +748,6 @@
   </si>
   <si>
     <t>strip</t>
-  </si>
-  <si>
-    <t>zip</t>
   </si>
   <si>
     <t>Adding items</t>
@@ -885,7 +1001,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -895,7 +1011,7 @@
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -905,7 +1021,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -914,10 +1030,22 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1206,7 +1334,7 @@
     <col customWidth="1" min="3" max="3" width="26.88"/>
     <col customWidth="1" min="4" max="4" width="35.38"/>
     <col customWidth="1" min="5" max="5" width="27.0"/>
-    <col customWidth="1" min="6" max="6" width="16.88"/>
+    <col customWidth="1" min="6" max="6" width="24.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1245,408 +1373,438 @@
       <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="9"/>
+        <v>16</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="9"/>
+        <v>28</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="6"/>
+        <v>34</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="9"/>
+        <v>40</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="H8" s="10" t="s">
-        <v>41</v>
+        <v>46</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="9"/>
+        <v>53</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="6"/>
+        <v>58</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="9"/>
+        <v>74</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F16" s="6"/>
+        <v>92</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="F17" s="13"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" s="6"/>
+        <v>103</v>
+      </c>
+      <c r="F18" s="14"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="9"/>
+        <v>107</v>
+      </c>
+      <c r="F19" s="13"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F20" s="6"/>
+        <v>110</v>
+      </c>
+      <c r="F20" s="14"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="9"/>
+        <v>113</v>
+      </c>
+      <c r="F21" s="13"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="F22" s="14"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F23" s="9"/>
+        <v>118</v>
+      </c>
+      <c r="F23" s="13"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="6"/>
+        <v>121</v>
+      </c>
+      <c r="F24" s="14"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" s="9"/>
+        <v>123</v>
+      </c>
+      <c r="F25" s="13"/>
     </row>
     <row r="26">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="6"/>
+        <v>124</v>
+      </c>
+      <c r="F26" s="14"/>
     </row>
     <row r="27">
       <c r="A27" s="7"/>
       <c r="B27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F27" s="9"/>
+        <v>125</v>
+      </c>
+      <c r="F27" s="13"/>
     </row>
     <row r="28">
-      <c r="E28" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="12"/>
+      <c r="E28" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" s="16"/>
     </row>
   </sheetData>
   <drawing r:id="rId2"/>
